--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.65.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.65.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.65.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.65.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,8 +431,8 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="50" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.65.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.65.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0065.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0065.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -601,16 +601,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L4: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: there are the following rules :â€” :</t>
+          <t>L57: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: 83 ； H</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L6: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: there are the following rules :â€”</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]58 EVIDENCE.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]58 EVIDENCE.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L27: symbol-only separator/garbage line :: 1850.</t>
@@ -645,14 +649,14 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
       <c r="E3" s="1" t="inlineStr"/>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>L54: candidate OCR token mismatch vs other OCR: "compos" vs "compel" :: Order Ã§ compos the production of the documents stated in</t>
+          <t>L54: candidate OCR token mismatch vs other OCR: "compos" vs "compel" :: Order ç compos the production of the documents stated in</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr"/>
@@ -660,14 +664,10 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L81: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN :: çŸ¥</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L85: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: PrÂ° ucâ€˜compellable to produce. The cases on the subject are</t>
-        </is>
-      </c>
+          <t>L81: stray/suspicious non-ASCII glyph(s): U+77E5 CJK UNIFIED IDEOGRAPH-77E5 | isolated marker/symbol line :: 知</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -719,7 +719,7 @@
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L82: isolated marker/symbol line :: 0</t>
+          <t>L81: stray/suspicious non-ASCII glyph(s): U+77E5 CJK UNIFIED IDEOGRAPH-77E5 | isolated marker/symbol line :: 知</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr"/>
@@ -747,7 +747,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -760,7 +760,11 @@
       <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
-      <c r="N5" s="1" t="inlineStr"/>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>L82: isolated marker/symbol line :: 0</t>
+        </is>
+      </c>
       <c r="O5" s="1" t="inlineStr"/>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
@@ -942,7 +946,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -981,7 +985,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1015,7 +1019,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
